--- a/artfynd/A 47165-2023 artfynd.xlsx
+++ b/artfynd/A 47165-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47165-2023 artfynd.xlsx
+++ b/artfynd/A 47165-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>75330791</v>
       </c>
       <c r="B2" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560912.0253369083</v>
+        <v>560912</v>
       </c>
       <c r="R2" t="n">
-        <v>7093912.982218334</v>
+        <v>7093913</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,12 +792,7 @@
         <v>97362930</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560801.4663428193</v>
+        <v>560801</v>
       </c>
       <c r="R3" t="n">
-        <v>7094054.520342926</v>
+        <v>7094055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2021-06-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,12 +898,7 @@
         <v>97362916</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560772.9904831154</v>
+        <v>560773</v>
       </c>
       <c r="R4" t="n">
-        <v>7094161.182207313</v>
+        <v>7094161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +963,9 @@
           <t>2021-06-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,6 +989,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97362950</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N Hållbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>560819</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7094244</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>

--- a/artfynd/A 47165-2023 artfynd.xlsx
+++ b/artfynd/A 47165-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,8 +1114,19 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362930</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>